--- a/XLSV/1sheetinitialXLSX.xlsx
+++ b/XLSV/1sheetinitialXLSX.xlsx
@@ -18,9 +18,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
-    <c r="A1" t="s">
-      <v>0</v>
-    </c>
+    <row r="3"/>
   </sheetData>
 </worksheet>
 </file>